--- a/business_surveys/008_pitch_explanation_survey--business_surveys.xlsx
+++ b/business_surveys/008_pitch_explanation_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -528,7 +528,11 @@
           <t>Introduction</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A brief introduction to the pitch</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,20 +542,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pitch</t>
+          <t>pitch_opinion</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pitch</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What did you think of the pitch?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select one</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,7 +569,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -589,15 +597,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>improvement</t>
+          <t>improvement_point</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>improvement</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What do you think is the main improvement point for the pitch?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select one</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -617,10 +629,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>suggestion</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Do you have any suggestions for the pitch?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please provide your suggestions</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -640,10 +656,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>next_steps</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What are the next steps for the pitch?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please provide your next steps</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -658,15 +678,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Do you have any other comments on the pitch?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please provide any additional comments</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,15 +705,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>additional_info</t>
+          <t>follow_up_info</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>additional_info</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>How can I follow up with you about the pitch?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Provide a preferred email address or phone number</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -709,10 +737,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Enter a valid email address</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -732,10 +764,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Phone Number</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Enter a valid phone number</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +786,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>next_steps</t>
+          <t>additional_info</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>next_steps</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Additional Information</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please provide any additional information</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -773,15 +813,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>next_steps</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>next_steps</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What is the status of the pitch?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please provide the current status</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -801,10 +845,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Follow-up</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>How can I follow up with you about the pitch?</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -819,15 +867,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>suggestion_phone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Your phone number</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Enter a valid phone number</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -842,246 +894,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>email_address</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Your email address</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Enter a valid email address</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>additional_info</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>additional_info</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>feedback</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>feedback</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>additional_info</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>additional_info</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>improvement</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>improvement</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>suggestion</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>suggestion</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>next_steps</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>next_steps</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,11 +924,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1126,102 +952,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>pitch_opinion_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>pitch_opinion_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>improvement_choices</t>
+          <t>improvement_point_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>improvement_choices</t>
+          <t>improvement_point_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>improvement_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>improvement_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
